--- a/JsonConverter/ExcelFiles/EquipmentData.xlsx
+++ b/JsonConverter/ExcelFiles/EquipmentData.xlsx
@@ -43,13 +43,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>BaseAtk</t>
+    <t>BaseAttack</t>
   </si>
   <si>
     <t>BaseHp</t>
   </si>
   <si>
-    <t>BaseDef</t>
+    <t>BaseDefense</t>
   </si>
   <si>
     <t>SkillId</t>
@@ -162,12 +162,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -176,11 +182,14 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -450,13 +459,13 @@
       <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F3" s="1" t="s">

--- a/JsonConverter/ExcelFiles/EquipmentData.xlsx
+++ b/JsonConverter/ExcelFiles/EquipmentData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="59">
   <si>
     <t>장비 고유id</t>
   </si>
@@ -28,9 +28,18 @@
     <t>기본 방어력</t>
   </si>
   <si>
+    <t>장비 종류
+Accessory
+Armor
+Weapon</t>
+  </si>
+  <si>
     <t>스킬 id</t>
   </si>
   <si>
+    <t>아이콘 이미지 경로</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
@@ -52,18 +61,30 @@
     <t>BaseDefense</t>
   </si>
   <si>
+    <t>EquipmentTypeString</t>
+  </si>
+  <si>
     <t>SkillId</t>
   </si>
   <si>
+    <t>IconPath</t>
+  </si>
+  <si>
     <t>Equipment_001</t>
   </si>
   <si>
     <t>줄무늬 잠옷</t>
   </si>
   <si>
+    <t>Armor</t>
+  </si>
+  <si>
     <t>Skill_101</t>
   </si>
   <si>
+    <t>UI/Equipments[Equipment_0]</t>
+  </si>
+  <si>
     <t>Equipment_002</t>
   </si>
   <si>
@@ -73,6 +94,9 @@
     <t>Skill_102</t>
   </si>
   <si>
+    <t>UI/Equipments[Equipment_1]</t>
+  </si>
+  <si>
     <t>Equipment_003</t>
   </si>
   <si>
@@ -82,6 +106,9 @@
     <t>Skill_103</t>
   </si>
   <si>
+    <t>UI/Equipments[Equipment_3]</t>
+  </si>
+  <si>
     <t>Equipment_004</t>
   </si>
   <si>
@@ -91,6 +118,9 @@
     <t>Skill_104</t>
   </si>
   <si>
+    <t>UI/Equipments[Equipment_4]</t>
+  </si>
+  <si>
     <t>Equipment_005</t>
   </si>
   <si>
@@ -100,6 +130,9 @@
     <t>Skill_105</t>
   </si>
   <si>
+    <t>UI/Equipments[Equipment_5]</t>
+  </si>
+  <si>
     <t>Equipment_006</t>
   </si>
   <si>
@@ -109,6 +142,9 @@
     <t>Skill_106</t>
   </si>
   <si>
+    <t>UI/Equipments[Equipment_6]</t>
+  </si>
+  <si>
     <t>Equipment_007</t>
   </si>
   <si>
@@ -118,6 +154,9 @@
     <t>Skill_107</t>
   </si>
   <si>
+    <t>UI/Equipments[Equipment_7]</t>
+  </si>
+  <si>
     <t>Equipment_008</t>
   </si>
   <si>
@@ -127,6 +166,9 @@
     <t>Skill_108</t>
   </si>
   <si>
+    <t>UI/Equipments[Equipment_8]</t>
+  </si>
+  <si>
     <t>Equipment_009</t>
   </si>
   <si>
@@ -136,6 +178,9 @@
     <t>Skill_109</t>
   </si>
   <si>
+    <t>UI/Equipments[Equipment_9]</t>
+  </si>
+  <si>
     <t>Equipment_010</t>
   </si>
   <si>
@@ -143,6 +188,9 @@
   </si>
   <si>
     <t>Skill_110</t>
+  </si>
+  <si>
+    <t>UI/Equipments[Equipment_10]</t>
   </si>
 </sst>
 </file>
@@ -410,6 +458,8 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="16.25"/>
+    <col customWidth="1" min="6" max="6" width="19.63"/>
+    <col customWidth="1" min="8" max="8" width="32.13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -431,53 +481,71 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1">
         <v>5.0</v>
@@ -489,15 +557,21 @@
         <v>2.0</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1">
         <v>8.0</v>
@@ -509,15 +583,21 @@
         <v>1.0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C6" s="1">
         <v>10.0</v>
@@ -529,15 +609,21 @@
         <v>4.0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C7" s="1">
         <v>4.0</v>
@@ -549,15 +635,21 @@
         <v>12.0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C8" s="1">
         <v>14.0</v>
@@ -569,15 +661,21 @@
         <v>3.0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C9" s="1">
         <v>16.0</v>
@@ -589,15 +687,21 @@
         <v>5.0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C10" s="1">
         <v>20.0</v>
@@ -609,15 +713,21 @@
         <v>8.0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C11" s="1">
         <v>24.0</v>
@@ -629,15 +739,21 @@
         <v>6.0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>37</v>
+        <v>20</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="C12" s="1">
         <v>28.0</v>
@@ -649,15 +765,21 @@
         <v>10.0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>40</v>
+        <v>20</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C13" s="1">
         <v>34.0</v>
@@ -669,7 +791,13 @@
         <v>14.0</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>43</v>
+        <v>20</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/JsonConverter/ExcelFiles/EquipmentData.xlsx
+++ b/JsonConverter/ExcelFiles/EquipmentData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="65">
   <si>
     <t>장비 고유id</t>
   </si>
@@ -40,6 +40,9 @@
     <t>아이콘 이미지 경로</t>
   </si>
   <si>
+    <t>등급</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
@@ -70,6 +73,9 @@
     <t>IconPath</t>
   </si>
   <si>
+    <t>Grade</t>
+  </si>
+  <si>
     <t>Equipment_001</t>
   </si>
   <si>
@@ -85,6 +91,9 @@
     <t>UI/Equipments[Equipment_0]</t>
   </si>
   <si>
+    <t>Rare</t>
+  </si>
+  <si>
     <t>Equipment_002</t>
   </si>
   <si>
@@ -121,6 +130,9 @@
     <t>UI/Equipments[Equipment_4]</t>
   </si>
   <si>
+    <t>Epic</t>
+  </si>
+  <si>
     <t>Equipment_005</t>
   </si>
   <si>
@@ -157,6 +169,9 @@
     <t>UI/Equipments[Equipment_7]</t>
   </si>
   <si>
+    <t>Unique</t>
+  </si>
+  <si>
     <t>Equipment_008</t>
   </si>
   <si>
@@ -191,6 +206,9 @@
   </si>
   <si>
     <t>UI/Equipments[Equipment_10]</t>
+  </si>
+  <si>
+    <t>Legendry</t>
   </si>
 </sst>
 </file>
@@ -487,65 +505,74 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
+      <c r="I2" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1">
         <v>5.0</v>
@@ -557,21 +584,24 @@
         <v>2.0</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C5" s="1">
         <v>8.0</v>
@@ -583,21 +613,24 @@
         <v>1.0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C6" s="1">
         <v>10.0</v>
@@ -609,21 +642,24 @@
         <v>4.0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C7" s="1">
         <v>4.0</v>
@@ -635,21 +671,24 @@
         <v>12.0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C8" s="1">
         <v>14.0</v>
@@ -661,21 +700,24 @@
         <v>3.0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C9" s="1">
         <v>16.0</v>
@@ -687,21 +729,24 @@
         <v>5.0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C10" s="1">
         <v>20.0</v>
@@ -713,21 +758,24 @@
         <v>8.0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C11" s="1">
         <v>24.0</v>
@@ -739,21 +787,24 @@
         <v>6.0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C12" s="1">
         <v>28.0</v>
@@ -765,21 +816,24 @@
         <v>10.0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C13" s="1">
         <v>34.0</v>
@@ -791,13 +845,16 @@
         <v>14.0</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/JsonConverter/ExcelFiles/EquipmentData.xlsx
+++ b/JsonConverter/ExcelFiles/EquipmentData.xlsx
@@ -11,12 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="67">
   <si>
     <t>장비 고유id</t>
   </si>
   <si>
     <t>이름</t>
+  </si>
+  <si>
+    <t>등급</t>
   </si>
   <si>
     <t>기본 공격력</t>
@@ -34,15 +37,15 @@
 Weapon</t>
   </si>
   <si>
-    <t>스킬 id</t>
+    <t>기본 스킬 id</t>
+  </si>
+  <si>
+    <t>액티브 스킬 id</t>
   </si>
   <si>
     <t>아이콘 이미지 경로</t>
   </si>
   <si>
-    <t>등급</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
@@ -55,6 +58,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>Grade</t>
+  </si>
+  <si>
     <t>BaseAttack</t>
   </si>
   <si>
@@ -67,21 +73,24 @@
     <t>EquipmentTypeString</t>
   </si>
   <si>
-    <t>SkillId</t>
+    <t>BaseSkillId</t>
+  </si>
+  <si>
+    <t>AciveSkillId</t>
   </si>
   <si>
     <t>IconPath</t>
   </si>
   <si>
-    <t>Grade</t>
-  </si>
-  <si>
     <t>Equipment_001</t>
   </si>
   <si>
     <t>줄무늬 잠옷</t>
   </si>
   <si>
+    <t>Rare</t>
+  </si>
+  <si>
     <t>Armor</t>
   </si>
   <si>
@@ -91,9 +100,6 @@
     <t>UI/Equipments[Equipment_0]</t>
   </si>
   <si>
-    <t>Rare</t>
-  </si>
-  <si>
     <t>Equipment_002</t>
   </si>
   <si>
@@ -124,15 +130,15 @@
     <t>두꺼운 외투</t>
   </si>
   <si>
+    <t>Epic</t>
+  </si>
+  <si>
     <t>Skill_104</t>
   </si>
   <si>
     <t>UI/Equipments[Equipment_4]</t>
   </si>
   <si>
-    <t>Epic</t>
-  </si>
-  <si>
     <t>Equipment_005</t>
   </si>
   <si>
@@ -163,15 +169,15 @@
     <t>은빛 갑주</t>
   </si>
   <si>
+    <t>Unique</t>
+  </si>
+  <si>
     <t>Skill_107</t>
   </si>
   <si>
     <t>UI/Equipments[Equipment_7]</t>
   </si>
   <si>
-    <t>Unique</t>
-  </si>
-  <si>
     <t>Equipment_008</t>
   </si>
   <si>
@@ -202,20 +208,20 @@
     <t>꿈의 파편 갑옷</t>
   </si>
   <si>
+    <t>Legendry</t>
+  </si>
+  <si>
     <t>Skill_110</t>
   </si>
   <si>
     <t>UI/Equipments[Equipment_10]</t>
-  </si>
-  <si>
-    <t>Legendry</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -227,19 +233,19 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFFF0000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -248,16 +254,17 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -476,8 +483,8 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="16.25"/>
-    <col customWidth="1" min="6" max="6" width="19.63"/>
-    <col customWidth="1" min="8" max="8" width="32.13"/>
+    <col customWidth="1" min="7" max="7" width="19.63"/>
+    <col customWidth="1" min="9" max="10" width="32.13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -508,353 +515,388 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>9</v>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="E3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="I3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="1">
+        <v>23</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="1">
         <v>5.0</v>
       </c>
-      <c r="D4" s="1">
+      <c r="E4" s="1">
         <v>10.0</v>
       </c>
-      <c r="E4" s="1">
+      <c r="F4" s="1">
         <v>2.0</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="G4" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="1">
+        <v>29</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="1">
         <v>8.0</v>
       </c>
-      <c r="D5" s="1">
+      <c r="E5" s="1">
         <v>5.0</v>
       </c>
-      <c r="E5" s="1">
+      <c r="F5" s="1">
         <v>1.0</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="G5" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="1">
+        <v>33</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="1">
         <v>10.0</v>
       </c>
-      <c r="D6" s="1">
+      <c r="E6" s="1">
         <v>15.0</v>
       </c>
-      <c r="E6" s="1">
+      <c r="F6" s="1">
         <v>4.0</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="G6" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="1">
+        <v>37</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="1">
         <v>4.0</v>
       </c>
-      <c r="D7" s="1">
+      <c r="E7" s="1">
         <v>40.0</v>
       </c>
-      <c r="E7" s="1">
+      <c r="F7" s="1">
         <v>12.0</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="G7" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="1">
+        <v>42</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="1">
         <v>14.0</v>
       </c>
-      <c r="D8" s="1">
+      <c r="E8" s="1">
         <v>10.0</v>
       </c>
-      <c r="E8" s="1">
+      <c r="F8" s="1">
         <v>3.0</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="G8" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
+      </c>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="1">
+        <v>46</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="1">
         <v>16.0</v>
       </c>
-      <c r="D9" s="1">
+      <c r="E9" s="1">
         <v>20.0</v>
       </c>
-      <c r="E9" s="1">
+      <c r="F9" s="1">
         <v>5.0</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="G9" s="1" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>38</v>
+        <v>47</v>
+      </c>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="1">
+        <v>50</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="1">
         <v>20.0</v>
       </c>
-      <c r="D10" s="1">
+      <c r="E10" s="1">
         <v>25.0</v>
       </c>
-      <c r="E10" s="1">
+      <c r="F10" s="1">
         <v>8.0</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="G10" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="1">
+        <v>55</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="1">
         <v>24.0</v>
       </c>
-      <c r="D11" s="1">
+      <c r="E11" s="1">
         <v>15.0</v>
       </c>
-      <c r="E11" s="1">
+      <c r="F11" s="1">
         <v>6.0</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="G11" s="1" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
+      </c>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="1">
+        <v>59</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="1">
         <v>28.0</v>
       </c>
-      <c r="D12" s="1">
+      <c r="E12" s="1">
         <v>30.0</v>
       </c>
-      <c r="E12" s="1">
+      <c r="F12" s="1">
         <v>10.0</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="G12" s="1" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>51</v>
+        <v>60</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" s="1">
+        <v>63</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="1">
         <v>34.0</v>
       </c>
-      <c r="D13" s="1">
+      <c r="E13" s="1">
         <v>40.0</v>
       </c>
-      <c r="E13" s="1">
+      <c r="F13" s="1">
         <v>14.0</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="G13" s="1" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/JsonConverter/ExcelFiles/EquipmentData.xlsx
+++ b/JsonConverter/ExcelFiles/EquipmentData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="시트1" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="95">
   <si>
     <t>장비 고유id</t>
   </si>
@@ -19,6 +19,9 @@
     <t>이름</t>
   </si>
   <si>
+    <t>등급</t>
+  </si>
+  <si>
     <t>기본 공격력</t>
   </si>
   <si>
@@ -26,6 +29,15 @@
   </si>
   <si>
     <t>기본 방어력</t>
+  </si>
+  <si>
+    <t>기본 치명타율</t>
+  </si>
+  <si>
+    <t>일반 스킬 가속</t>
+  </si>
+  <si>
+    <t>특수 스킬 가속</t>
   </si>
   <si>
     <t>장비 종류
@@ -34,12 +46,18 @@
 Weapon</t>
   </si>
   <si>
-    <t>스킬 id</t>
+    <t>기본 스킬 id</t>
+  </si>
+  <si>
+    <t>장비 스킬 id</t>
   </si>
   <si>
     <t>아이콘 이미지 경로</t>
   </si>
   <si>
+    <t>설명</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
@@ -52,6 +70,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>Grade</t>
+  </si>
+  <si>
     <t>BaseAttack</t>
   </si>
   <si>
@@ -61,21 +82,39 @@
     <t>BaseDefense</t>
   </si>
   <si>
+    <t>BaseCriticalChance</t>
+  </si>
+  <si>
+    <t>BasicAttackHaste</t>
+  </si>
+  <si>
+    <t>BasicActiveSkillHaste</t>
+  </si>
+  <si>
     <t>EquipmentTypeString</t>
   </si>
   <si>
-    <t>SkillId</t>
+    <t>BaseSkillId</t>
+  </si>
+  <si>
+    <t>AciveSkillId</t>
   </si>
   <si>
     <t>IconPath</t>
   </si>
   <si>
-    <t>Equipment_001</t>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Equipment_Armor_001</t>
   </si>
   <si>
     <t>줄무늬 잠옷</t>
   </si>
   <si>
+    <t>Rare</t>
+  </si>
+  <si>
     <t>Armor</t>
   </si>
   <si>
@@ -85,7 +124,7 @@
     <t>UI/Equipments[Equipment_0]</t>
   </si>
   <si>
-    <t>Equipment_002</t>
+    <t>Equipment_Armor_002</t>
   </si>
   <si>
     <t>구겨진 셔츠</t>
@@ -97,7 +136,7 @@
     <t>UI/Equipments[Equipment_1]</t>
   </si>
   <si>
-    <t>Equipment_003</t>
+    <t>Equipment_Armor_003</t>
   </si>
   <si>
     <t>견습생 로브</t>
@@ -109,19 +148,22 @@
     <t>UI/Equipments[Equipment_3]</t>
   </si>
   <si>
-    <t>Equipment_004</t>
+    <t>Equipment_Armor_004</t>
   </si>
   <si>
     <t>두꺼운 외투</t>
   </si>
   <si>
+    <t>Epic</t>
+  </si>
+  <si>
     <t>Skill_104</t>
   </si>
   <si>
     <t>UI/Equipments[Equipment_4]</t>
   </si>
   <si>
-    <t>Equipment_005</t>
+    <t>Equipment_Armor_005</t>
   </si>
   <si>
     <t>사냥꾼 재킷</t>
@@ -133,7 +175,7 @@
     <t>UI/Equipments[Equipment_5]</t>
   </si>
   <si>
-    <t>Equipment_006</t>
+    <t>Equipment_Armor_006</t>
   </si>
   <si>
     <t>몽상가의 로브</t>
@@ -145,19 +187,22 @@
     <t>UI/Equipments[Equipment_6]</t>
   </si>
   <si>
-    <t>Equipment_007</t>
+    <t>Equipment_Armor_007</t>
   </si>
   <si>
     <t>은빛 갑주</t>
   </si>
   <si>
+    <t>Unique</t>
+  </si>
+  <si>
     <t>Skill_107</t>
   </si>
   <si>
     <t>UI/Equipments[Equipment_7]</t>
   </si>
   <si>
-    <t>Equipment_008</t>
+    <t>Equipment_Armor_008</t>
   </si>
   <si>
     <t>수면술사의 망토</t>
@@ -169,7 +214,7 @@
     <t>UI/Equipments[Equipment_8]</t>
   </si>
   <si>
-    <t>Equipment_009</t>
+    <t>Equipment_Armor_009</t>
   </si>
   <si>
     <t>별빛 드레스</t>
@@ -181,36 +226,110 @@
     <t>UI/Equipments[Equipment_9]</t>
   </si>
   <si>
-    <t>Equipment_010</t>
+    <t>Equipment_Armor_010</t>
   </si>
   <si>
     <t>꿈의 파편 갑옷</t>
   </si>
   <si>
+    <t>Legendary</t>
+  </si>
+  <si>
     <t>Skill_110</t>
   </si>
   <si>
     <t>UI/Equipments[Equipment_10]</t>
+  </si>
+  <si>
+    <t>Equipment_Weapon_001</t>
+  </si>
+  <si>
+    <t>무기1</t>
+  </si>
+  <si>
+    <t>Weapon</t>
+  </si>
+  <si>
+    <t>UI/Equipments[Equipment_28]</t>
+  </si>
+  <si>
+    <t>Equipment_Weapon_002</t>
+  </si>
+  <si>
+    <t>무기2</t>
+  </si>
+  <si>
+    <t>UI/Equipments[Equipment_26]</t>
+  </si>
+  <si>
+    <t>Equipment_Weapon_003</t>
+  </si>
+  <si>
+    <t>무기3</t>
+  </si>
+  <si>
+    <t>UI/Equipments[Equipment_37]</t>
+  </si>
+  <si>
+    <t>Equipment_Accessory_001</t>
+  </si>
+  <si>
+    <t>악세서리1</t>
+  </si>
+  <si>
+    <t>Accessory</t>
+  </si>
+  <si>
+    <t>UI/Equipments[Equipment_70]</t>
+  </si>
+  <si>
+    <t>Equipment_Accessory_002</t>
+  </si>
+  <si>
+    <t>악세서리2</t>
+  </si>
+  <si>
+    <t>UI/Equipments[Equipment_71]</t>
+  </si>
+  <si>
+    <t>Equipment_Accessory_003</t>
+  </si>
+  <si>
+    <t>악세서리3</t>
+  </si>
+  <si>
+    <t>UI/Equipments[Equipment_69]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="4">
     <font>
-      <sz val="10.0"/>
+      <sz val="11.0"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Carlito"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11.0"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Carlito"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -219,25 +338,60 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFFF0000"/>
+        <fgColor rgb="FFB6D7A8"/>
+        <bgColor rgb="FFB6D7A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -273,40 +427,40 @@
         <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="467886"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Carlito"/>
+        <a:ea typeface="Carlito"/>
+        <a:cs typeface="Carlito"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Carlito"/>
+        <a:ea typeface="Carlito"/>
+        <a:cs typeface="Carlito"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -453,16 +607,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="16.25"/>
-    <col customWidth="1" min="6" max="6" width="19.63"/>
-    <col customWidth="1" min="8" max="8" width="32.13"/>
+    <col customWidth="1" min="1" max="2" width="22.0"/>
+    <col customWidth="1" min="3" max="3" width="14.0"/>
+    <col customWidth="1" min="4" max="6" width="16.0"/>
+    <col customWidth="1" min="7" max="7" width="24.0"/>
+    <col customWidth="1" min="8" max="9" width="26.0"/>
+    <col customWidth="1" min="10" max="10" width="24.0"/>
+    <col customWidth="1" min="11" max="12" width="18.0"/>
+    <col customWidth="1" min="13" max="14" width="34.0"/>
+    <col customWidth="1" min="15" max="26" width="8.63"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="33.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -481,326 +641,1713 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2">
+    <row r="2" ht="33.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="33.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
+        <v>19</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="1">
+    <row r="4" ht="24.0" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="5">
         <v>5.0</v>
       </c>
-      <c r="D4" s="1">
+      <c r="E4" s="5">
         <v>10.0</v>
       </c>
-      <c r="E4" s="1">
+      <c r="F4" s="5">
         <v>2.0</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="G4" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="6"/>
+      <c r="M4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="N4" s="4"/>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="1">
+    <row r="5" ht="24.0" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="5">
         <v>8.0</v>
       </c>
-      <c r="D5" s="1">
+      <c r="E5" s="5">
         <v>5.0</v>
       </c>
-      <c r="E5" s="1">
+      <c r="F5" s="5">
         <v>1.0</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="G5" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5" s="6"/>
+      <c r="M5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" s="4"/>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="1">
+    <row r="6" ht="24.0" customHeight="1">
+      <c r="A6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="5">
         <v>10.0</v>
       </c>
-      <c r="D6" s="1">
+      <c r="E6" s="5">
         <v>15.0</v>
       </c>
-      <c r="E6" s="1">
+      <c r="F6" s="5">
         <v>4.0</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="G6" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="L6" s="6"/>
+      <c r="M6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="N6" s="4"/>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="1" t="s">
+    <row r="7" ht="24.0" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>40.0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>12.0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="L7" s="6"/>
+      <c r="M7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="4"/>
+    </row>
+    <row r="8" ht="24.0" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="5">
+        <v>14.0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="L8" s="6"/>
+      <c r="M8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="N8" s="4"/>
+    </row>
+    <row r="9" ht="24.0" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="5">
+        <v>16.0</v>
+      </c>
+      <c r="E9" s="5">
+        <v>20.0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>5.0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="L9" s="6"/>
+      <c r="M9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="N9" s="4"/>
+    </row>
+    <row r="10" ht="24.0" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="5">
+        <v>20.0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>25.0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>8.0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="L10" s="6"/>
+      <c r="M10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="N10" s="4"/>
+    </row>
+    <row r="11" ht="24.0" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="5">
+        <v>24.0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>15.0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>6.0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="L11" s="6"/>
+      <c r="M11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="N11" s="4"/>
+    </row>
+    <row r="12" ht="24.0" customHeight="1">
+      <c r="A12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="5">
+        <v>28.0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>30.0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="L12" s="6"/>
+      <c r="M12" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="N12" s="4"/>
+    </row>
+    <row r="13" ht="24.0" customHeight="1">
+      <c r="A13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="5">
+        <v>34.0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>40.0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>14.0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="L13" s="6"/>
+      <c r="M13" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="N13" s="4"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="1">
+      <c r="D14" s="5">
+        <v>24.0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="5">
+        <v>28.0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>5.0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="5">
+        <v>34.0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>15.0</v>
+      </c>
+      <c r="F16" s="5">
         <v>4.0</v>
       </c>
-      <c r="D7" s="1">
-        <v>40.0</v>
-      </c>
-      <c r="E7" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>34</v>
+      <c r="G16" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="D8" s="1">
+    <row r="17">
+      <c r="A17" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="5">
+        <v>5.0</v>
+      </c>
+      <c r="E17" s="5">
         <v>10.0</v>
       </c>
-      <c r="E8" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>38</v>
+      <c r="F17" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="D9" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="E9" s="1">
+    <row r="18">
+      <c r="A18" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="5">
+        <v>8.0</v>
+      </c>
+      <c r="E18" s="5">
         <v>5.0</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>42</v>
+      <c r="F18" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="G18" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H18" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I18" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>91</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="D10" s="1">
-        <v>25.0</v>
-      </c>
-      <c r="E10" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>46</v>
+    <row r="19">
+      <c r="A19" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="E19" s="5">
+        <v>15.0</v>
+      </c>
+      <c r="F19" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="G19" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H19" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I19" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="D11" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="E11" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="1">
-        <v>28.0</v>
-      </c>
-      <c r="D12" s="1">
-        <v>30.0</v>
-      </c>
-      <c r="E12" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="1">
-        <v>34.0</v>
-      </c>
-      <c r="D13" s="1">
-        <v>40.0</v>
-      </c>
-      <c r="E13" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/EquipmentData.xlsx
+++ b/JsonConverter/ExcelFiles/EquipmentData.xlsx
@@ -31,7 +31,7 @@
     <t>기본 방어력</t>
   </si>
   <si>
-    <t>기본 치명타율</t>
+    <t>기본 치명타 확률</t>
   </si>
   <si>
     <t>일반 스킬 가속</t>
@@ -97,7 +97,7 @@
     <t>BaseSkillId</t>
   </si>
   <si>
-    <t>AciveSkillId</t>
+    <t>AcitveSkillId</t>
   </si>
   <si>
     <t>IconPath</t>
@@ -744,7 +744,7 @@
       <c r="K3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="2" t="s">
         <v>27</v>
       </c>
       <c r="M3" s="1" t="s">

--- a/JsonConverter/ExcelFiles/EquipmentData.xlsx
+++ b/JsonConverter/ExcelFiles/EquipmentData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="103">
   <si>
     <t>장비 고유id</t>
   </si>
@@ -299,6 +299,30 @@
   </si>
   <si>
     <t>UI/Equipments[Equipment_69]</t>
+  </si>
+  <si>
+    <t>Equipment_Armor_011</t>
+  </si>
+  <si>
+    <t>용사의 갑옷</t>
+  </si>
+  <si>
+    <t>UI/Equipments[Equipment_15]</t>
+  </si>
+  <si>
+    <t>Equipment_Weapon_004</t>
+  </si>
+  <si>
+    <t>용사의 검</t>
+  </si>
+  <si>
+    <t>UI/Equipments[Equipment_51]</t>
+  </si>
+  <si>
+    <t>Equipment_Accessory_004</t>
+  </si>
+  <si>
+    <t>용사의 반지</t>
   </si>
 </sst>
 </file>
@@ -1364,8 +1388,111 @@
         <v>94</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="E20" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="F20" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="G20" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H20" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I20" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="E21" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="F21" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="G21" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H21" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I21" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="E22" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="F22" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="G22" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H22" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I22" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1"/>
     <row r="25" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/EquipmentData.xlsx
+++ b/JsonConverter/ExcelFiles/EquipmentData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="103">
   <si>
     <t>장비 고유id</t>
   </si>
@@ -31,7 +31,7 @@
     <t>기본 방어력</t>
   </si>
   <si>
-    <t>기본 치명타율</t>
+    <t>기본 치명타 확률</t>
   </si>
   <si>
     <t>일반 스킬 가속</t>
@@ -97,7 +97,7 @@
     <t>BaseSkillId</t>
   </si>
   <si>
-    <t>AciveSkillId</t>
+    <t>AcitveSkillId</t>
   </si>
   <si>
     <t>IconPath</t>
@@ -299,6 +299,30 @@
   </si>
   <si>
     <t>UI/Equipments[Equipment_69]</t>
+  </si>
+  <si>
+    <t>Equipment_Armor_011</t>
+  </si>
+  <si>
+    <t>용사의 갑옷</t>
+  </si>
+  <si>
+    <t>UI/Equipments[Equipment_15]</t>
+  </si>
+  <si>
+    <t>Equipment_Weapon_004</t>
+  </si>
+  <si>
+    <t>용사의 검</t>
+  </si>
+  <si>
+    <t>UI/Equipments[Equipment_51]</t>
+  </si>
+  <si>
+    <t>Equipment_Accessory_004</t>
+  </si>
+  <si>
+    <t>용사의 반지</t>
   </si>
 </sst>
 </file>
@@ -744,7 +768,7 @@
       <c r="K3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="2" t="s">
         <v>27</v>
       </c>
       <c r="M3" s="1" t="s">
@@ -1364,8 +1388,111 @@
         <v>94</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="E20" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="F20" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="G20" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H20" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I20" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="E21" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="F21" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="G21" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H21" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I21" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="E22" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="F22" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="G22" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H22" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I22" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1"/>
     <row r="25" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/EquipmentData.xlsx
+++ b/JsonConverter/ExcelFiles/EquipmentData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="110">
   <si>
     <t>장비 고유id</t>
   </si>
@@ -37,7 +37,7 @@
     <t>일반 스킬 가속</t>
   </si>
   <si>
-    <t>특수 스킬 가속</t>
+    <t>고유 스킬 가속</t>
   </si>
   <si>
     <t>장비 종류
@@ -49,15 +49,18 @@
     <t>기본 스킬 id</t>
   </si>
   <si>
-    <t>장비 스킬 id</t>
-  </si>
-  <si>
-    <t>아이콘 이미지 경로</t>
+    <t>고유 스킬 ID</t>
+  </si>
+  <si>
+    <t>아이콘 스프라이트 Addressable Key</t>
   </si>
   <si>
     <t>설명</t>
   </si>
   <si>
+    <t>애니메이션 세트 Addressable Key</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
@@ -88,7 +91,7 @@
     <t>BasicAttackHaste</t>
   </si>
   <si>
-    <t>BasicActiveSkillHaste</t>
+    <t>SignatureSkillHaste</t>
   </si>
   <si>
     <t>EquipmentTypeString</t>
@@ -97,15 +100,18 @@
     <t>BaseSkillId</t>
   </si>
   <si>
-    <t>AcitveSkillId</t>
-  </si>
-  <si>
-    <t>IconPath</t>
+    <t>SignatureSkillId</t>
+  </si>
+  <si>
+    <t>IconSpriteAddressableKey</t>
   </si>
   <si>
     <t>Description</t>
   </si>
   <si>
+    <t>AnimationSetKey</t>
+  </si>
+  <si>
     <t>Equipment_Armor_001</t>
   </si>
   <si>
@@ -121,7 +127,7 @@
     <t>Skill_101</t>
   </si>
   <si>
-    <t>UI/Equipments[Equipment_0]</t>
+    <t>Sprite/armor_001_icon</t>
   </si>
   <si>
     <t>Equipment_Armor_002</t>
@@ -133,7 +139,7 @@
     <t>Skill_102</t>
   </si>
   <si>
-    <t>UI/Equipments[Equipment_1]</t>
+    <t>Sprite/armor_002_icon</t>
   </si>
   <si>
     <t>Equipment_Armor_003</t>
@@ -145,7 +151,7 @@
     <t>Skill_103</t>
   </si>
   <si>
-    <t>UI/Equipments[Equipment_3]</t>
+    <t>Sprite/armor_003_icon</t>
   </si>
   <si>
     <t>Equipment_Armor_004</t>
@@ -160,7 +166,7 @@
     <t>Skill_104</t>
   </si>
   <si>
-    <t>UI/Equipments[Equipment_4]</t>
+    <t>Sprite/armor_004_icon</t>
   </si>
   <si>
     <t>Equipment_Armor_005</t>
@@ -172,7 +178,7 @@
     <t>Skill_105</t>
   </si>
   <si>
-    <t>UI/Equipments[Equipment_5]</t>
+    <t>Sprite/armor_005_icon</t>
   </si>
   <si>
     <t>Equipment_Armor_006</t>
@@ -184,7 +190,7 @@
     <t>Skill_106</t>
   </si>
   <si>
-    <t>UI/Equipments[Equipment_6]</t>
+    <t>Sprite/armor_006_icon</t>
   </si>
   <si>
     <t>Equipment_Armor_007</t>
@@ -199,7 +205,7 @@
     <t>Skill_107</t>
   </si>
   <si>
-    <t>UI/Equipments[Equipment_7]</t>
+    <t>Sprite/armor_007_icon</t>
   </si>
   <si>
     <t>Equipment_Armor_008</t>
@@ -211,7 +217,7 @@
     <t>Skill_108</t>
   </si>
   <si>
-    <t>UI/Equipments[Equipment_8]</t>
+    <t>Sprite/armor_008_icon</t>
   </si>
   <si>
     <t>Equipment_Armor_009</t>
@@ -223,7 +229,7 @@
     <t>Skill_109</t>
   </si>
   <si>
-    <t>UI/Equipments[Equipment_9]</t>
+    <t>Sprite/armor_009_icon</t>
   </si>
   <si>
     <t>Equipment_Armor_010</t>
@@ -238,7 +244,7 @@
     <t>Skill_110</t>
   </si>
   <si>
-    <t>UI/Equipments[Equipment_10]</t>
+    <t>Sprite/armor_010_icon</t>
   </si>
   <si>
     <t>Equipment_Weapon_001</t>
@@ -250,7 +256,10 @@
     <t>Weapon</t>
   </si>
   <si>
-    <t>UI/Equipments[Equipment_28]</t>
+    <t>Sprite/weapon_001_icon</t>
+  </si>
+  <si>
+    <t>Anim/weapon_001</t>
   </si>
   <si>
     <t>Equipment_Weapon_002</t>
@@ -259,7 +268,10 @@
     <t>무기2</t>
   </si>
   <si>
-    <t>UI/Equipments[Equipment_26]</t>
+    <t>Sprite/weapon_002_icon</t>
+  </si>
+  <si>
+    <t>Anim/weapon_002</t>
   </si>
   <si>
     <t>Equipment_Weapon_003</t>
@@ -268,7 +280,10 @@
     <t>무기3</t>
   </si>
   <si>
-    <t>UI/Equipments[Equipment_37]</t>
+    <t>Sprite/weapon_003_icon</t>
+  </si>
+  <si>
+    <t>Anim/weapon_003</t>
   </si>
   <si>
     <t>Equipment_Accessory_001</t>
@@ -280,7 +295,7 @@
     <t>Accessory</t>
   </si>
   <si>
-    <t>UI/Equipments[Equipment_70]</t>
+    <t>Sprite/accessory_001_icon</t>
   </si>
   <si>
     <t>Equipment_Accessory_002</t>
@@ -289,7 +304,7 @@
     <t>악세서리2</t>
   </si>
   <si>
-    <t>UI/Equipments[Equipment_71]</t>
+    <t>Sprite/accessory_002_icon</t>
   </si>
   <si>
     <t>Equipment_Accessory_003</t>
@@ -298,7 +313,7 @@
     <t>악세서리3</t>
   </si>
   <si>
-    <t>UI/Equipments[Equipment_69]</t>
+    <t>Sprite/accessory_003_icon</t>
   </si>
   <si>
     <t>Equipment_Armor_011</t>
@@ -307,7 +322,7 @@
     <t>용사의 갑옷</t>
   </si>
   <si>
-    <t>UI/Equipments[Equipment_15]</t>
+    <t>Sprite/armor_011_icon</t>
   </si>
   <si>
     <t>Equipment_Weapon_004</t>
@@ -316,20 +331,26 @@
     <t>용사의 검</t>
   </si>
   <si>
-    <t>UI/Equipments[Equipment_51]</t>
+    <t>Sprite/weapon_004_icon</t>
+  </si>
+  <si>
+    <t>Anim/weapon_004</t>
   </si>
   <si>
     <t>Equipment_Accessory_004</t>
   </si>
   <si>
     <t>용사의 반지</t>
+  </si>
+  <si>
+    <t>Sprite/accessory_004_icon</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
@@ -348,9 +369,13 @@
       <name val="Carlito"/>
     </font>
     <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Carlito"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -393,18 +418,12 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
@@ -415,9 +434,10 @@
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -643,7 +663,7 @@
     <col customWidth="1" min="10" max="10" width="24.0"/>
     <col customWidth="1" min="11" max="12" width="18.0"/>
     <col customWidth="1" min="13" max="14" width="34.0"/>
-    <col customWidth="1" min="15" max="26" width="8.63"/>
+    <col customWidth="1" min="15" max="15" width="8.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="33.75" customHeight="1">
@@ -665,13 +685,13 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -680,7 +700,7 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -688,810 +708,873 @@
       </c>
       <c r="N1" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="2" ht="33.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" ht="33.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="I3" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="J3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="L3" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="M3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="4" ht="24.0" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="5">
+      <c r="B4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="3">
         <v>5.0</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="3">
         <v>10.0</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="3">
         <v>2.0</v>
       </c>
-      <c r="G4" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="H4" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="6"/>
-      <c r="M4" s="4" t="s">
+      <c r="G4" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="N4" s="4"/>
+      <c r="K4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4" s="4"/>
+      <c r="M4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4" s="2"/>
+      <c r="O4" s="5"/>
     </row>
     <row r="5" ht="24.0" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="5">
+      <c r="A5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="3">
         <v>8.0</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="3">
         <v>5.0</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="3">
         <v>1.0</v>
       </c>
-      <c r="G5" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="H5" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="L5" s="6"/>
-      <c r="M5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5" s="4"/>
+      <c r="G5" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" s="4"/>
+      <c r="M5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="5"/>
     </row>
     <row r="6" ht="24.0" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="5">
+      <c r="A6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="3">
         <v>10.0</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="3">
         <v>15.0</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="3">
         <v>4.0</v>
       </c>
-      <c r="G6" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="H6" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="L6" s="6"/>
-      <c r="M6" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="N6" s="4"/>
+      <c r="G6" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L6" s="4"/>
+      <c r="M6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="5"/>
     </row>
     <row r="7" ht="24.0" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="5">
+      <c r="B7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="3">
         <v>4.0</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="3">
         <v>40.0</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="3">
         <v>12.0</v>
       </c>
-      <c r="G7" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="H7" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="I7" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="L7" s="6"/>
-      <c r="M7" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="N7" s="4"/>
+      <c r="G7" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="4"/>
+      <c r="M7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N7" s="2"/>
+      <c r="O7" s="5"/>
     </row>
     <row r="8" ht="24.0" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="A8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="3">
         <v>14.0</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="3">
         <v>10.0</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="3">
         <v>3.0</v>
       </c>
-      <c r="G8" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="H8" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="I8" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="L8" s="6"/>
-      <c r="M8" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="N8" s="4"/>
+      <c r="G8" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="L8" s="4"/>
+      <c r="M8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N8" s="2"/>
+      <c r="O8" s="5"/>
     </row>
     <row r="9" ht="24.0" customHeight="1">
-      <c r="A9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="A9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="3">
         <v>16.0</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="3">
         <v>20.0</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="3">
         <v>5.0</v>
       </c>
-      <c r="G9" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="H9" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="I9" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L9" s="6"/>
-      <c r="M9" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="N9" s="4"/>
+      <c r="G9" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L9" s="4"/>
+      <c r="M9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="N9" s="2"/>
+      <c r="O9" s="5"/>
     </row>
     <row r="10" ht="24.0" customHeight="1">
-      <c r="A10" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="A10" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="5">
+      <c r="B10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="3">
         <v>20.0</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="3">
         <v>25.0</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="3">
         <v>8.0</v>
       </c>
-      <c r="G10" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="H10" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="I10" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="L10" s="6"/>
-      <c r="M10" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="N10" s="4"/>
+      <c r="G10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="L10" s="4"/>
+      <c r="M10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="5"/>
     </row>
     <row r="11" ht="24.0" customHeight="1">
-      <c r="A11" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="A11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="3">
         <v>24.0</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="3">
         <v>15.0</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="3">
         <v>6.0</v>
       </c>
-      <c r="G11" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="H11" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="I11" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="L11" s="6"/>
-      <c r="M11" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="N11" s="4"/>
+      <c r="G11" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="L11" s="4"/>
+      <c r="M11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="5"/>
     </row>
     <row r="12" ht="24.0" customHeight="1">
-      <c r="A12" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="A12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="3">
         <v>28.0</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="3">
         <v>30.0</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="3">
         <v>10.0</v>
       </c>
-      <c r="G12" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="H12" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="I12" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="L12" s="6"/>
-      <c r="M12" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="N12" s="4"/>
+      <c r="G12" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="L12" s="4"/>
+      <c r="M12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="5"/>
     </row>
     <row r="13" ht="24.0" customHeight="1">
-      <c r="A13" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="5">
+      <c r="B13" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="3">
         <v>34.0</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="3">
         <v>40.0</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="3">
         <v>14.0</v>
       </c>
-      <c r="G13" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="H13" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="I13" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="L13" s="6"/>
-      <c r="M13" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="N13" s="4"/>
+      <c r="G13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L13" s="4"/>
+      <c r="M13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="5"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="A14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="3">
         <v>24.0</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="3">
         <v>10.0</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="3">
         <v>2.0</v>
       </c>
-      <c r="G14" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="H14" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="I14" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>78</v>
+      <c r="G14" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="3">
+        <v>28.0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J15" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="5">
-        <v>28.0</v>
-      </c>
-      <c r="E15" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="F15" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="G15" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="H15" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="I15" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>81</v>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="A16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="3">
         <v>34.0</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="3">
         <v>15.0</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="3">
         <v>4.0</v>
       </c>
-      <c r="G16" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="H16" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="I16" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>84</v>
+      <c r="G16" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I16" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="A17" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="3">
         <v>5.0</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="3">
         <v>10.0</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="3">
         <v>2.0</v>
       </c>
-      <c r="G17" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="H17" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="I17" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>88</v>
-      </c>
+      <c r="G17" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="A18" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="3">
         <v>8.0</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="3">
         <v>5.0</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="3">
         <v>1.0</v>
       </c>
-      <c r="G18" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="H18" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="I18" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>91</v>
-      </c>
+      <c r="G18" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="E19" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="F19" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J19" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" s="5">
-        <v>10.0</v>
-      </c>
-      <c r="E19" s="5">
-        <v>15.0</v>
-      </c>
-      <c r="F19" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="G19" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="H19" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="I19" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>94</v>
-      </c>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="E20" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="F20" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="G20" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="H20" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="I20" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>97</v>
-      </c>
+      <c r="A20" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="E21" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="F21" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="G21" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="H21" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="I21" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>100</v>
+      <c r="A21" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="E22" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="F22" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="G22" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="H22" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="I22" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>94</v>
-      </c>
+      <c r="A22" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/EquipmentData.xlsx
+++ b/JsonConverter/ExcelFiles/EquipmentData.xlsx
@@ -112,7 +112,7 @@
     <t>AnimationSetKey</t>
   </si>
   <si>
-    <t>Equipment_Armor_001</t>
+    <t>equipment_armor_001</t>
   </si>
   <si>
     <t>줄무늬 잠옷</t>
@@ -127,10 +127,10 @@
     <t>Skill_101</t>
   </si>
   <si>
-    <t>Sprite/armor_001_icon</t>
-  </si>
-  <si>
-    <t>Equipment_Armor_002</t>
+    <t>Sprite/Equipment[Aromor_001]</t>
+  </si>
+  <si>
+    <t>equipment_armor_002</t>
   </si>
   <si>
     <t>구겨진 셔츠</t>
@@ -139,10 +139,10 @@
     <t>Skill_102</t>
   </si>
   <si>
-    <t>Sprite/armor_002_icon</t>
-  </si>
-  <si>
-    <t>Equipment_Armor_003</t>
+    <t>Sprite/Equipment[Aromor_002]</t>
+  </si>
+  <si>
+    <t>equipment_armor_003</t>
   </si>
   <si>
     <t>견습생 로브</t>
@@ -151,10 +151,10 @@
     <t>Skill_103</t>
   </si>
   <si>
-    <t>Sprite/armor_003_icon</t>
-  </si>
-  <si>
-    <t>Equipment_Armor_004</t>
+    <t>Sprite/Equipment[Aromor_003]</t>
+  </si>
+  <si>
+    <t>equipment_armor_004</t>
   </si>
   <si>
     <t>두꺼운 외투</t>
@@ -166,10 +166,10 @@
     <t>Skill_104</t>
   </si>
   <si>
-    <t>Sprite/armor_004_icon</t>
-  </si>
-  <si>
-    <t>Equipment_Armor_005</t>
+    <t>Sprite/Equipment[Aromor_004]</t>
+  </si>
+  <si>
+    <t>equipment_armor_005</t>
   </si>
   <si>
     <t>사냥꾼 재킷</t>
@@ -178,10 +178,10 @@
     <t>Skill_105</t>
   </si>
   <si>
-    <t>Sprite/armor_005_icon</t>
-  </si>
-  <si>
-    <t>Equipment_Armor_006</t>
+    <t>Sprite/Equipment[Aromor_005]</t>
+  </si>
+  <si>
+    <t>equipment_armor_006</t>
   </si>
   <si>
     <t>몽상가의 로브</t>
@@ -190,10 +190,10 @@
     <t>Skill_106</t>
   </si>
   <si>
-    <t>Sprite/armor_006_icon</t>
-  </si>
-  <si>
-    <t>Equipment_Armor_007</t>
+    <t>Sprite/Equipment[Aromor_006]</t>
+  </si>
+  <si>
+    <t>equipment_armor_007</t>
   </si>
   <si>
     <t>은빛 갑주</t>
@@ -205,10 +205,10 @@
     <t>Skill_107</t>
   </si>
   <si>
-    <t>Sprite/armor_007_icon</t>
-  </si>
-  <si>
-    <t>Equipment_Armor_008</t>
+    <t>Sprite/Equipment[Aromor_007]</t>
+  </si>
+  <si>
+    <t>equipment_armor_008</t>
   </si>
   <si>
     <t>수면술사의 망토</t>
@@ -217,10 +217,10 @@
     <t>Skill_108</t>
   </si>
   <si>
-    <t>Sprite/armor_008_icon</t>
-  </si>
-  <si>
-    <t>Equipment_Armor_009</t>
+    <t>Sprite/Equipment[Aromor_008]</t>
+  </si>
+  <si>
+    <t>equipment_armor_009</t>
   </si>
   <si>
     <t>별빛 드레스</t>
@@ -229,10 +229,10 @@
     <t>Skill_109</t>
   </si>
   <si>
-    <t>Sprite/armor_009_icon</t>
-  </si>
-  <si>
-    <t>Equipment_Armor_010</t>
+    <t>Sprite/Equipment[Aromor_009]</t>
+  </si>
+  <si>
+    <t>equipment_armor_010</t>
   </si>
   <si>
     <t>꿈의 파편 갑옷</t>
@@ -244,10 +244,10 @@
     <t>Skill_110</t>
   </si>
   <si>
-    <t>Sprite/armor_010_icon</t>
-  </si>
-  <si>
-    <t>Equipment_Weapon_001</t>
+    <t>Sprite/Equipment[Aromor_010]</t>
+  </si>
+  <si>
+    <t>equipment_weapon_001</t>
   </si>
   <si>
     <t>무기1</t>
@@ -256,37 +256,37 @@
     <t>Weapon</t>
   </si>
   <si>
-    <t>Sprite/weapon_001_icon</t>
+    <t>Sprite/Equipment[Weapon_001]</t>
   </si>
   <si>
     <t>Anim/weapon_001</t>
   </si>
   <si>
-    <t>Equipment_Weapon_002</t>
+    <t>equipment_weapon_002</t>
   </si>
   <si>
     <t>무기2</t>
   </si>
   <si>
-    <t>Sprite/weapon_002_icon</t>
+    <t>Sprite/Equipment[Weapon_002]</t>
   </si>
   <si>
     <t>Anim/weapon_002</t>
   </si>
   <si>
-    <t>Equipment_Weapon_003</t>
+    <t>equipment_weapon_003</t>
   </si>
   <si>
     <t>무기3</t>
   </si>
   <si>
-    <t>Sprite/weapon_003_icon</t>
+    <t>Sprite/Equipment[Weapon_003]</t>
   </si>
   <si>
     <t>Anim/weapon_003</t>
   </si>
   <si>
-    <t>Equipment_Accessory_001</t>
+    <t>equipment_accessory_001</t>
   </si>
   <si>
     <t>악세서리1</t>
@@ -295,55 +295,55 @@
     <t>Accessory</t>
   </si>
   <si>
-    <t>Sprite/accessory_001_icon</t>
-  </si>
-  <si>
-    <t>Equipment_Accessory_002</t>
+    <t>Sprite/Equipment[Accessory_001]</t>
+  </si>
+  <si>
+    <t>equipment_accessory_002</t>
   </si>
   <si>
     <t>악세서리2</t>
   </si>
   <si>
-    <t>Sprite/accessory_002_icon</t>
-  </si>
-  <si>
-    <t>Equipment_Accessory_003</t>
+    <t>Sprite/Equipment[Accessory_002]</t>
+  </si>
+  <si>
+    <t>equipment_accessory_003</t>
   </si>
   <si>
     <t>악세서리3</t>
   </si>
   <si>
-    <t>Sprite/accessory_003_icon</t>
-  </si>
-  <si>
-    <t>Equipment_Armor_011</t>
+    <t>Sprite/Equipment[Accessory_003]</t>
+  </si>
+  <si>
+    <t>equipment_armor_011</t>
   </si>
   <si>
     <t>용사의 갑옷</t>
   </si>
   <si>
-    <t>Sprite/armor_011_icon</t>
-  </si>
-  <si>
-    <t>Equipment_Weapon_004</t>
+    <t>Sprite/Equipment[Aromor_011]</t>
+  </si>
+  <si>
+    <t>equipment_weapon_004</t>
   </si>
   <si>
     <t>용사의 검</t>
   </si>
   <si>
-    <t>Sprite/weapon_004_icon</t>
+    <t>Sprite/Equipment[Weapon_004]</t>
   </si>
   <si>
     <t>Anim/weapon_004</t>
   </si>
   <si>
-    <t>Equipment_Accessory_004</t>
+    <t>equipment_accessory_004</t>
   </si>
   <si>
     <t>용사의 반지</t>
   </si>
   <si>
-    <t>Sprite/accessory_004_icon</t>
+    <t>Sprite/Equipment[Accessory_004]</t>
   </si>
 </sst>
 </file>
@@ -418,12 +418,15 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
@@ -438,6 +441,9 @@
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -656,17 +662,21 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="2" width="22.0"/>
-    <col customWidth="1" min="3" max="3" width="14.0"/>
-    <col customWidth="1" min="4" max="6" width="16.0"/>
-    <col customWidth="1" min="7" max="7" width="24.0"/>
-    <col customWidth="1" min="8" max="9" width="26.0"/>
-    <col customWidth="1" min="10" max="10" width="24.0"/>
+    <col customWidth="1" min="3" max="3" width="12.75"/>
+    <col customWidth="1" min="4" max="4" width="13.63"/>
+    <col customWidth="1" min="5" max="5" width="13.38"/>
+    <col customWidth="1" min="6" max="6" width="13.63"/>
+    <col customWidth="1" min="7" max="7" width="18.88"/>
+    <col customWidth="1" min="8" max="8" width="19.25"/>
+    <col customWidth="1" min="9" max="9" width="18.25"/>
+    <col customWidth="1" min="10" max="10" width="19.25"/>
     <col customWidth="1" min="11" max="12" width="18.0"/>
-    <col customWidth="1" min="13" max="14" width="34.0"/>
-    <col customWidth="1" min="15" max="15" width="8.63"/>
+    <col customWidth="1" min="13" max="13" width="26.0"/>
+    <col customWidth="1" min="14" max="14" width="20.88"/>
+    <col customWidth="1" min="15" max="15" width="17.88"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33.75" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -811,450 +821,450 @@
       <c r="A4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="4">
         <v>5.0</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="4">
         <v>10.0</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="4">
         <v>2.0</v>
       </c>
-      <c r="G4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J4" s="4" t="s">
+      <c r="G4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="L4" s="4"/>
+      <c r="L4" s="5"/>
       <c r="M4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N4" s="2"/>
-      <c r="O4" s="5"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="6"/>
     </row>
     <row r="5" ht="24.0" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="4">
         <v>8.0</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="4">
         <v>5.0</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="4">
         <v>1.0</v>
       </c>
-      <c r="G5" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I5" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J5" s="4" t="s">
+      <c r="G5" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="L5" s="4"/>
+      <c r="L5" s="5"/>
       <c r="M5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="5"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="6"/>
     </row>
     <row r="6" ht="24.0" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="4">
         <v>10.0</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="4">
         <v>15.0</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="4">
         <v>4.0</v>
       </c>
-      <c r="G6" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J6" s="4" t="s">
+      <c r="G6" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="4"/>
+      <c r="L6" s="5"/>
       <c r="M6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N6" s="2"/>
-      <c r="O6" s="5"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="6"/>
     </row>
     <row r="7" ht="24.0" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="4">
         <v>4.0</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="4">
         <v>40.0</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="4">
         <v>12.0</v>
       </c>
-      <c r="G7" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I7" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J7" s="4" t="s">
+      <c r="G7" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="4"/>
+      <c r="L7" s="5"/>
       <c r="M7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N7" s="2"/>
-      <c r="O7" s="5"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="6"/>
     </row>
     <row r="8" ht="24.0" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="4">
         <v>14.0</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="4">
         <v>10.0</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="4">
         <v>3.0</v>
       </c>
-      <c r="G8" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J8" s="4" t="s">
+      <c r="G8" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="L8" s="4"/>
+      <c r="L8" s="5"/>
       <c r="M8" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="N8" s="2"/>
-      <c r="O8" s="5"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="6"/>
     </row>
     <row r="9" ht="24.0" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="4">
         <v>16.0</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="4">
         <v>20.0</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="4">
         <v>5.0</v>
       </c>
-      <c r="G9" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I9" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J9" s="4" t="s">
+      <c r="G9" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="L9" s="4"/>
+      <c r="L9" s="5"/>
       <c r="M9" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="N9" s="2"/>
-      <c r="O9" s="5"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="6"/>
     </row>
     <row r="10" ht="24.0" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="4">
         <v>20.0</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="4">
         <v>25.0</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="4">
         <v>8.0</v>
       </c>
-      <c r="G10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J10" s="4" t="s">
+      <c r="G10" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J10" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="L10" s="4"/>
+      <c r="L10" s="5"/>
       <c r="M10" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="5"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="6"/>
     </row>
     <row r="11" ht="24.0" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="4">
         <v>24.0</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="4">
         <v>15.0</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="4">
         <v>6.0</v>
       </c>
-      <c r="G11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J11" s="4" t="s">
+      <c r="G11" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J11" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="L11" s="4"/>
+      <c r="L11" s="5"/>
       <c r="M11" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="5"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="6"/>
     </row>
     <row r="12" ht="24.0" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="4">
         <v>28.0</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="4">
         <v>30.0</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="4">
         <v>10.0</v>
       </c>
-      <c r="G12" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H12" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I12" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J12" s="4" t="s">
+      <c r="G12" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J12" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="L12" s="4"/>
+      <c r="L12" s="5"/>
       <c r="M12" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="5"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="6"/>
     </row>
     <row r="13" ht="24.0" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="4">
         <v>34.0</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="4">
         <v>40.0</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="4">
         <v>14.0</v>
       </c>
-      <c r="G13" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H13" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I13" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J13" s="4" t="s">
+      <c r="G13" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J13" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="L13" s="4"/>
+      <c r="L13" s="5"/>
       <c r="M13" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="N13" s="2"/>
-      <c r="O13" s="5"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="6"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="4">
         <v>24.0</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="4">
         <v>10.0</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="4">
         <v>2.0</v>
       </c>
-      <c r="G14" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J14" s="6" t="s">
+      <c r="G14" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J14" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
       <c r="M14" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5" t="s">
+      <c r="N14" s="6"/>
+      <c r="O14" s="6" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1262,40 +1272,40 @@
       <c r="A15" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="4">
         <v>28.0</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="4">
         <v>5.0</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="4">
         <v>1.0</v>
       </c>
-      <c r="G15" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J15" s="6" t="s">
+      <c r="G15" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
       <c r="M15" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5" t="s">
+      <c r="N15" s="6"/>
+      <c r="O15" s="6" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1303,278 +1313,278 @@
       <c r="A16" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="4">
         <v>34.0</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="4">
         <v>15.0</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="4">
         <v>4.0</v>
       </c>
-      <c r="G16" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H16" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I16" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J16" s="6" t="s">
+      <c r="G16" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J16" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
       <c r="M16" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5" t="s">
+      <c r="N16" s="6"/>
+      <c r="O16" s="6" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="4">
         <v>5.0</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="4">
         <v>10.0</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="4">
         <v>2.0</v>
       </c>
-      <c r="G17" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H17" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I17" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J17" s="6" t="s">
+      <c r="G17" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J17" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
       <c r="M17" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="4">
         <v>8.0</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="4">
         <v>5.0</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="4">
         <v>1.0</v>
       </c>
-      <c r="G18" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H18" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I18" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J18" s="6" t="s">
+      <c r="G18" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I18" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J18" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
       <c r="M18" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="4">
         <v>10.0</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="4">
         <v>15.0</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="4">
         <v>4.0</v>
       </c>
-      <c r="G19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J19" s="6" t="s">
+      <c r="G19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J19" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
       <c r="M19" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J20" s="4" t="s">
+      <c r="D20" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E20" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F20" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="G20" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H20" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I20" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J20" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
       <c r="M20" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="E21" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="F21" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="G21" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H21" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J21" s="6" t="s">
+      <c r="D21" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E21" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F21" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H21" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I21" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J21" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
       <c r="M21" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5" t="s">
+      <c r="N21" s="6"/>
+      <c r="O21" s="6" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D22" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J22" s="6" t="s">
+      <c r="D22" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E22" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F22" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="G22" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H22" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I22" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J22" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
       <c r="M22" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/EquipmentData.xlsx
+++ b/JsonConverter/ExcelFiles/EquipmentData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="84">
   <si>
     <t>장비 고유id</t>
   </si>
@@ -97,7 +97,7 @@
     <t>EquipmentTypeString</t>
   </si>
   <si>
-    <t>BaseSkillId</t>
+    <t>BasicAttackSkillId</t>
   </si>
   <si>
     <t>SignatureSkillId</t>
@@ -112,31 +112,73 @@
     <t>AnimationSetKey</t>
   </si>
   <si>
+    <t>equipment_accessory_001</t>
+  </si>
+  <si>
+    <t>초보 용사의 반지</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>Accessory</t>
+  </si>
+  <si>
+    <t>Sprite/Equipment[Accessory_001]</t>
+  </si>
+  <si>
+    <t>equipment_accessory_002</t>
+  </si>
+  <si>
+    <t>화가의 팔레트</t>
+  </si>
+  <si>
+    <t>Legendary</t>
+  </si>
+  <si>
+    <t>Sprite/Equipment[Accessory_002]</t>
+  </si>
+  <si>
+    <t>equipment_accessory_003</t>
+  </si>
+  <si>
+    <t>학자의 아뮬렛</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>Sprite/Equipment[Accessory_003]</t>
+  </si>
+  <si>
+    <t>equipment_accessory_004</t>
+  </si>
+  <si>
+    <t>무사의 맹약 반지</t>
+  </si>
+  <si>
+    <t>Unique</t>
+  </si>
+  <si>
+    <t>Sprite/Equipment[Accessory_004]</t>
+  </si>
+  <si>
     <t>equipment_armor_001</t>
   </si>
   <si>
-    <t>줄무늬 잠옷</t>
-  </si>
-  <si>
-    <t>Rare</t>
+    <t>초보 용사의 갑옷</t>
   </si>
   <si>
     <t>Armor</t>
   </si>
   <si>
-    <t>Skill_101</t>
-  </si>
-  <si>
     <t>Sprite/Equipment[Aromor_001]</t>
   </si>
   <si>
     <t>equipment_armor_002</t>
   </si>
   <si>
-    <t>구겨진 셔츠</t>
-  </si>
-  <si>
-    <t>Skill_102</t>
+    <t>몽상가의 로브</t>
   </si>
   <si>
     <t>Sprite/Equipment[Aromor_002]</t>
@@ -145,10 +187,7 @@
     <t>equipment_armor_003</t>
   </si>
   <si>
-    <t>견습생 로브</t>
-  </si>
-  <si>
-    <t>Skill_103</t>
+    <t>학자의 로브</t>
   </si>
   <si>
     <t>Sprite/Equipment[Aromor_003]</t>
@@ -157,105 +196,27 @@
     <t>equipment_armor_004</t>
   </si>
   <si>
-    <t>두꺼운 외투</t>
-  </si>
-  <si>
-    <t>Epic</t>
-  </si>
-  <si>
-    <t>Skill_104</t>
+    <t>무사의 갑주</t>
   </si>
   <si>
     <t>Sprite/Equipment[Aromor_004]</t>
   </si>
   <si>
-    <t>equipment_armor_005</t>
-  </si>
-  <si>
-    <t>사냥꾼 재킷</t>
-  </si>
-  <si>
-    <t>Skill_105</t>
-  </si>
-  <si>
-    <t>Sprite/Equipment[Aromor_005]</t>
-  </si>
-  <si>
-    <t>equipment_armor_006</t>
-  </si>
-  <si>
-    <t>몽상가의 로브</t>
-  </si>
-  <si>
-    <t>Skill_106</t>
-  </si>
-  <si>
-    <t>Sprite/Equipment[Aromor_006]</t>
-  </si>
-  <si>
-    <t>equipment_armor_007</t>
-  </si>
-  <si>
-    <t>은빛 갑주</t>
-  </si>
-  <si>
-    <t>Unique</t>
-  </si>
-  <si>
-    <t>Skill_107</t>
-  </si>
-  <si>
-    <t>Sprite/Equipment[Aromor_007]</t>
-  </si>
-  <si>
-    <t>equipment_armor_008</t>
-  </si>
-  <si>
-    <t>수면술사의 망토</t>
-  </si>
-  <si>
-    <t>Skill_108</t>
-  </si>
-  <si>
-    <t>Sprite/Equipment[Aromor_008]</t>
-  </si>
-  <si>
-    <t>equipment_armor_009</t>
-  </si>
-  <si>
-    <t>별빛 드레스</t>
-  </si>
-  <si>
-    <t>Skill_109</t>
-  </si>
-  <si>
-    <t>Sprite/Equipment[Aromor_009]</t>
-  </si>
-  <si>
-    <t>equipment_armor_010</t>
-  </si>
-  <si>
-    <t>꿈의 파편 갑옷</t>
-  </si>
-  <si>
-    <t>Legendary</t>
-  </si>
-  <si>
-    <t>Skill_110</t>
-  </si>
-  <si>
-    <t>Sprite/Equipment[Aromor_010]</t>
-  </si>
-  <si>
     <t>equipment_weapon_001</t>
   </si>
   <si>
-    <t>무기1</t>
+    <t>초보 용사의 검</t>
   </si>
   <si>
     <t>Weapon</t>
   </si>
   <si>
+    <t>skill_player_001_basic</t>
+  </si>
+  <si>
+    <t>skill_weapon_001</t>
+  </si>
+  <si>
     <t>Sprite/Equipment[Weapon_001]</t>
   </si>
   <si>
@@ -265,7 +226,10 @@
     <t>equipment_weapon_002</t>
   </si>
   <si>
-    <t>무기2</t>
+    <t>유랑 화가의 붓</t>
+  </si>
+  <si>
+    <t>skill_weapon_002</t>
   </si>
   <si>
     <t>Sprite/Equipment[Weapon_002]</t>
@@ -277,7 +241,10 @@
     <t>equipment_weapon_003</t>
   </si>
   <si>
-    <t>무기3</t>
+    <t>학자의 마법봉</t>
+  </si>
+  <si>
+    <t>skill_weapon_003</t>
   </si>
   <si>
     <t>Sprite/Equipment[Weapon_003]</t>
@@ -286,70 +253,28 @@
     <t>Anim/weapon_003</t>
   </si>
   <si>
-    <t>equipment_accessory_001</t>
-  </si>
-  <si>
-    <t>악세서리1</t>
-  </si>
-  <si>
-    <t>Accessory</t>
-  </si>
-  <si>
-    <t>Sprite/Equipment[Accessory_001]</t>
-  </si>
-  <si>
-    <t>equipment_accessory_002</t>
-  </si>
-  <si>
-    <t>악세서리2</t>
-  </si>
-  <si>
-    <t>Sprite/Equipment[Accessory_002]</t>
-  </si>
-  <si>
-    <t>equipment_accessory_003</t>
-  </si>
-  <si>
-    <t>악세서리3</t>
-  </si>
-  <si>
-    <t>Sprite/Equipment[Accessory_003]</t>
-  </si>
-  <si>
-    <t>equipment_armor_011</t>
-  </si>
-  <si>
-    <t>용사의 갑옷</t>
-  </si>
-  <si>
-    <t>Sprite/Equipment[Aromor_011]</t>
-  </si>
-  <si>
     <t>equipment_weapon_004</t>
   </si>
   <si>
-    <t>용사의 검</t>
+    <t>무사의 카타나</t>
+  </si>
+  <si>
+    <t>skill_weapon_004</t>
   </si>
   <si>
     <t>Sprite/Equipment[Weapon_004]</t>
   </si>
   <si>
     <t>Anim/weapon_004</t>
-  </si>
-  <si>
-    <t>equipment_accessory_004</t>
-  </si>
-  <si>
-    <t>용사의 반지</t>
-  </si>
-  <si>
-    <t>Sprite/Equipment[Accessory_004]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.###"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <sz val="11.0"/>
@@ -364,6 +289,10 @@
       <name val="Carlito"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
       <sz val="11.0"/>
       <color rgb="FF1F1F1F"/>
       <name val="Carlito"/>
@@ -371,10 +300,6 @@
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <color theme="1"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -418,31 +343,43 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -801,7 +738,7 @@
       <c r="J3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="2" t="s">
         <v>27</v>
       </c>
       <c r="L3" s="1" t="s">
@@ -818,773 +755,615 @@
       </c>
     </row>
     <row r="4" ht="24.0" customHeight="1">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="E4" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="F4" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="H4" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="I4" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="J4" s="5" t="s">
+      <c r="D4" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0.08</v>
+      </c>
+      <c r="H4" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="L4" s="5"/>
-      <c r="M4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N4" s="3"/>
-      <c r="O4" s="6"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="8"/>
     </row>
     <row r="5" ht="24.0" customHeight="1">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="4">
-        <v>8.0</v>
-      </c>
-      <c r="E5" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F5" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="H5" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="I5" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="J5" s="5" t="s">
+      <c r="D5" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>0.177</v>
+      </c>
+      <c r="H5" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="I5" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="L5" s="5"/>
-      <c r="M5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N5" s="3"/>
-      <c r="O5" s="6"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="8"/>
     </row>
     <row r="6" ht="24.0" customHeight="1">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="E6" s="4">
-        <v>15.0</v>
-      </c>
-      <c r="F6" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="H6" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="I6" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="J6" s="5" t="s">
+      <c r="D6" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0.11</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="I6" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="5"/>
-      <c r="M6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="N6" s="3"/>
-      <c r="O6" s="6"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="8"/>
     </row>
     <row r="7" ht="24.0" customHeight="1">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="G7" s="7">
+        <v>0.14</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="E7" s="4">
-        <v>40.0</v>
-      </c>
-      <c r="F7" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="G7" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="H7" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="I7" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="L7" s="5"/>
-      <c r="M7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N7" s="3"/>
-      <c r="O7" s="6"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="8"/>
     </row>
     <row r="8" ht="24.0" customHeight="1">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="E8" s="6">
+        <v>150.0</v>
+      </c>
+      <c r="F8" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="J8" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="4">
-        <v>14.0</v>
-      </c>
-      <c r="E8" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="F8" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="G8" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="H8" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="I8" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="L8" s="5"/>
-      <c r="M8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="N8" s="3"/>
-      <c r="O8" s="6"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="8"/>
     </row>
     <row r="9" ht="24.0" customHeight="1">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="E9" s="6">
+        <v>450.0</v>
+      </c>
+      <c r="F9" s="6">
+        <v>55.0</v>
+      </c>
+      <c r="G9" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="I9" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="4">
-        <v>16.0</v>
-      </c>
-      <c r="E9" s="4">
-        <v>20.0</v>
-      </c>
-      <c r="F9" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="G9" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="H9" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="I9" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="L9" s="5"/>
-      <c r="M9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="N9" s="3"/>
-      <c r="O9" s="6"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="8"/>
     </row>
     <row r="10" ht="24.0" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="4">
-        <v>20.0</v>
-      </c>
-      <c r="E10" s="4">
-        <v>25.0</v>
-      </c>
-      <c r="F10" s="4">
-        <v>8.0</v>
-      </c>
-      <c r="G10" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="H10" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="I10" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="L10" s="5"/>
-      <c r="M10" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="N10" s="3"/>
-      <c r="O10" s="6"/>
+      <c r="A10" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="E10" s="6">
+        <v>260.0</v>
+      </c>
+      <c r="F10" s="6">
+        <v>32.0</v>
+      </c>
+      <c r="G10" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="I10" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="N10" s="5"/>
+      <c r="O10" s="8"/>
     </row>
     <row r="11" ht="24.0" customHeight="1">
-      <c r="A11" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="A11" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="E11" s="6">
+        <v>350.0</v>
+      </c>
+      <c r="F11" s="6">
+        <v>43.0</v>
+      </c>
+      <c r="G11" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="4">
-        <v>24.0</v>
-      </c>
-      <c r="E11" s="4">
-        <v>15.0</v>
-      </c>
-      <c r="F11" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="G11" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="H11" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="I11" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="L11" s="5"/>
-      <c r="M11" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="N11" s="3"/>
-      <c r="O11" s="6"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="8"/>
     </row>
     <row r="12" ht="24.0" customHeight="1">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="6">
+        <v>55.0</v>
+      </c>
+      <c r="E12" s="6">
+        <v>40.0</v>
+      </c>
+      <c r="F12" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="G12" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H12" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="I12" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D12" s="4">
-        <v>28.0</v>
-      </c>
-      <c r="E12" s="4">
-        <v>30.0</v>
-      </c>
-      <c r="F12" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="G12" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="H12" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="I12" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="L12" s="5"/>
-      <c r="M12" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="N12" s="3"/>
-      <c r="O12" s="6"/>
     </row>
     <row r="13" ht="24.0" customHeight="1">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="6">
+        <v>160.0</v>
+      </c>
+      <c r="E13" s="6">
+        <v>120.0</v>
+      </c>
+      <c r="F13" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="G13" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H13" s="6">
+        <v>12.0</v>
+      </c>
+      <c r="I13" s="6">
+        <v>12.0</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="M13" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="N13" s="5"/>
+      <c r="O13" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D13" s="4">
-        <v>34.0</v>
-      </c>
-      <c r="E13" s="4">
-        <v>40.0</v>
-      </c>
-      <c r="F13" s="4">
-        <v>14.0</v>
-      </c>
-      <c r="G13" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="H13" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="I13" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="L13" s="5"/>
-      <c r="M13" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="N13" s="3"/>
-      <c r="O13" s="6"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="6">
+        <v>90.0</v>
+      </c>
+      <c r="E14" s="6">
+        <v>65.0</v>
+      </c>
+      <c r="F14" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="G14" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H14" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="I14" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="L14" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="M14" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="N14" s="5"/>
+      <c r="O14" s="8" t="s">
         <v>78</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="4">
-        <v>24.0</v>
-      </c>
-      <c r="E14" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="F14" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="G14" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="H14" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="I14" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="6">
+        <v>125.0</v>
+      </c>
+      <c r="E15" s="6">
+        <v>90.0</v>
+      </c>
+      <c r="F15" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="G15" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H15" s="6">
+        <v>10.0</v>
+      </c>
+      <c r="I15" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="L15" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="M15" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="N15" s="8"/>
+      <c r="O15" s="12" t="s">
         <v>83</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="4">
-        <v>28.0</v>
-      </c>
-      <c r="E15" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F15" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G15" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="H15" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="I15" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" s="4">
-        <v>34.0</v>
-      </c>
-      <c r="E16" s="4">
-        <v>15.0</v>
-      </c>
-      <c r="F16" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="G16" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="H16" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="I16" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6" t="s">
-        <v>89</v>
-      </c>
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="E17" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="F17" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="G17" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="H17" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="I17" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" s="4">
-        <v>8.0</v>
-      </c>
-      <c r="E18" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F18" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G18" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="H18" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="I18" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="E19" s="4">
-        <v>15.0</v>
-      </c>
-      <c r="F19" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="G19" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="H19" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="I19" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="N19" s="6"/>
-      <c r="O19" s="6"/>
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="E20" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="F20" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="G20" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="H20" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="I20" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="N20" s="6"/>
-      <c r="O20" s="6"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="E21" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="F21" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="G21" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="H21" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="I21" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="N21" s="6"/>
-      <c r="O21" s="6" t="s">
-        <v>106</v>
-      </c>
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="E22" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="F22" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="G22" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="H22" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="I22" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/EquipmentData.xlsx
+++ b/JsonConverter/ExcelFiles/EquipmentData.xlsx
@@ -343,7 +343,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -359,6 +359,9 @@
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="center"/>
@@ -765,33 +768,33 @@
         <v>34</v>
       </c>
       <c r="D4" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="E4" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="F4" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="G4" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="E4" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="F4" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="G4" s="8">
         <v>0.08</v>
       </c>
-      <c r="H4" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="I4" s="6">
+      <c r="H4" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="I4" s="7">
         <v>0.0</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
       <c r="M4" s="5" t="s">
         <v>36</v>
       </c>
       <c r="N4" s="5"/>
-      <c r="O4" s="8"/>
+      <c r="O4" s="9"/>
     </row>
     <row r="5" ht="24.0" customHeight="1">
       <c r="A5" s="3" t="s">
@@ -804,33 +807,33 @@
         <v>39</v>
       </c>
       <c r="D5" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="E5" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="F5" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="G5" s="7">
+        <v>10.0</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="G5" s="8">
         <v>0.177</v>
       </c>
-      <c r="H5" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="I5" s="6">
+      <c r="H5" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="I5" s="7">
         <v>0.0</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
       <c r="M5" s="5" t="s">
         <v>40</v>
       </c>
       <c r="N5" s="5"/>
-      <c r="O5" s="8"/>
+      <c r="O5" s="9"/>
     </row>
     <row r="6" ht="24.0" customHeight="1">
       <c r="A6" s="3" t="s">
@@ -843,33 +846,33 @@
         <v>43</v>
       </c>
       <c r="D6" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="E6" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="F6" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="G6" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="E6" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="G6" s="8">
         <v>0.11</v>
       </c>
-      <c r="H6" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="I6" s="6">
+      <c r="H6" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="I6" s="7">
         <v>0.0</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
       <c r="M6" s="5" t="s">
         <v>44</v>
       </c>
       <c r="N6" s="5"/>
-      <c r="O6" s="8"/>
+      <c r="O6" s="9"/>
     </row>
     <row r="7" ht="24.0" customHeight="1">
       <c r="A7" s="3" t="s">
@@ -882,36 +885,36 @@
         <v>47</v>
       </c>
       <c r="D7" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="F7" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="G7" s="7">
+        <v>7.0</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="G7" s="8">
         <v>0.14</v>
       </c>
-      <c r="H7" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="I7" s="6">
+      <c r="H7" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="I7" s="7">
         <v>0.0</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="9" t="s">
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="10" t="s">
         <v>48</v>
       </c>
       <c r="N7" s="5"/>
-      <c r="O7" s="8"/>
+      <c r="O7" s="9"/>
     </row>
     <row r="8" ht="24.0" customHeight="1">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="10" t="s">
         <v>49</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -920,37 +923,37 @@
       <c r="C8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="E8" s="6">
+      <c r="D8" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E8" s="7">
         <v>150.0</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="7">
         <v>20.0</v>
       </c>
-      <c r="G8" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="H8" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="I8" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="J8" s="10" t="s">
+      <c r="G8" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="H8" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="J8" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
       <c r="M8" s="5" t="s">
         <v>52</v>
       </c>
       <c r="N8" s="5"/>
-      <c r="O8" s="8"/>
+      <c r="O8" s="9"/>
     </row>
     <row r="9" ht="24.0" customHeight="1">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="10" t="s">
         <v>53</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -959,37 +962,37 @@
       <c r="C9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="E9" s="6">
+      <c r="D9" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E9" s="7">
         <v>450.0</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="7">
         <v>55.0</v>
       </c>
-      <c r="G9" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="H9" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="I9" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="J9" s="10" t="s">
+      <c r="G9" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="H9" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="I9" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
       <c r="M9" s="5" t="s">
         <v>55</v>
       </c>
       <c r="N9" s="5"/>
-      <c r="O9" s="8"/>
+      <c r="O9" s="9"/>
     </row>
     <row r="10" ht="24.0" customHeight="1">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B10" s="5" t="s">
@@ -998,37 +1001,37 @@
       <c r="C10" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="E10" s="6">
+      <c r="D10" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E10" s="7">
         <v>260.0</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="7">
         <v>32.0</v>
       </c>
-      <c r="G10" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="H10" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="I10" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="J10" s="10" t="s">
+      <c r="G10" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="H10" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="I10" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="J10" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
       <c r="M10" s="5" t="s">
         <v>58</v>
       </c>
       <c r="N10" s="5"/>
-      <c r="O10" s="8"/>
+      <c r="O10" s="9"/>
     </row>
     <row r="11" ht="24.0" customHeight="1">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="10" t="s">
         <v>59</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -1037,37 +1040,37 @@
       <c r="C11" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="E11" s="6">
+      <c r="D11" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="E11" s="7">
         <v>350.0</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="7">
         <v>43.0</v>
       </c>
-      <c r="G11" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="H11" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="I11" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="J11" s="10" t="s">
+      <c r="G11" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="H11" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="J11" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="9" t="s">
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="10" t="s">
         <v>61</v>
       </c>
       <c r="N11" s="5"/>
-      <c r="O11" s="8"/>
+      <c r="O11" s="9"/>
     </row>
     <row r="12" ht="24.0" customHeight="1">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="10" t="s">
         <v>62</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -1076,43 +1079,43 @@
       <c r="C12" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="7">
         <v>55.0</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="7">
         <v>40.0</v>
       </c>
-      <c r="F12" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="G12" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="H12" s="6">
+      <c r="F12" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="G12" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="H12" s="7">
         <v>4.0</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="7">
         <v>3.0</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K12" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="L12" s="12" t="s">
+      <c r="L12" s="13" t="s">
         <v>66</v>
       </c>
       <c r="M12" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8" t="s">
+      <c r="N12" s="9"/>
+      <c r="O12" s="9" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="13" ht="24.0" customHeight="1">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="10" t="s">
         <v>69</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -1121,43 +1124,43 @@
       <c r="C13" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="7">
         <v>160.0</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="7">
         <v>120.0</v>
       </c>
-      <c r="F13" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="G13" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="H13" s="6">
+      <c r="F13" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="H13" s="7">
         <v>12.0</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="7">
         <v>12.0</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="K13" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="L13" s="12" t="s">
+      <c r="L13" s="13" t="s">
         <v>71</v>
       </c>
       <c r="M13" s="5" t="s">
         <v>72</v>
       </c>
       <c r="N13" s="5"/>
-      <c r="O13" s="8" t="s">
+      <c r="O13" s="9" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="10" t="s">
         <v>74</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -1166,43 +1169,43 @@
       <c r="C14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="7">
         <v>90.0</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="7">
         <v>65.0</v>
       </c>
-      <c r="F14" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="G14" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="H14" s="6">
+      <c r="F14" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="G14" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="H14" s="7">
         <v>6.0</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="7">
         <v>8.0</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="K14" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="L14" s="12" t="s">
+      <c r="L14" s="13" t="s">
         <v>76</v>
       </c>
       <c r="M14" s="5" t="s">
         <v>77</v>
       </c>
       <c r="N14" s="5"/>
-      <c r="O14" s="8" t="s">
+      <c r="O14" s="9" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="10" t="s">
         <v>79</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -1211,38 +1214,38 @@
       <c r="C15" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="7">
         <v>125.0</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="7">
         <v>90.0</v>
       </c>
-      <c r="F15" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="G15" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="H15" s="6">
+      <c r="F15" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="H15" s="7">
         <v>10.0</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="7">
         <v>6.0</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="K15" s="11" t="s">
+      <c r="K15" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="L15" s="12" t="s">
+      <c r="L15" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="M15" s="9" t="s">
+      <c r="M15" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="N15" s="8"/>
-      <c r="O15" s="12" t="s">
+      <c r="N15" s="9"/>
+      <c r="O15" s="13" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1250,120 +1253,120 @@
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
       <c r="M16" s="5"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
     </row>
     <row r="17">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
       <c r="M17" s="5"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
     </row>
     <row r="18">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
     </row>
     <row r="19">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
     </row>
     <row r="20">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
       <c r="M20" s="5"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
       <c r="M21" s="5"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
       <c r="M22" s="5"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1"/>
